--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084530CE-F158-4415-8757-893A65208302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C4C04D-F1E3-4E81-BEF1-3C60DD1DEB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6345" yWindow="300" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>Planification</t>
   </si>
@@ -148,6 +148,15 @@
   </si>
   <si>
     <t>10 min</t>
+  </si>
+  <si>
+    <t>35 min</t>
+  </si>
+  <si>
+    <t>Analyse</t>
+  </si>
+  <si>
+    <t>J'ai fais mon analyse dans le rapport</t>
   </si>
 </sst>
 </file>
@@ -367,6 +376,57 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -410,57 +470,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -801,319 +810,308 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="32"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="16" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="17"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="23" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="19"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="36"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="20" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="23" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="36"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="20" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="19"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="36"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="19"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="36"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="27"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="19"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="23" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="29"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1130,6 +1128,17 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1145,769 +1154,754 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="32" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="33"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46262</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="30" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="31"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="32" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="33"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46262</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="30" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="30" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="31"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="33"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="31"/>
+      <c r="A7" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="33"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="31"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="33"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="31"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="33"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="31"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="33"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="31"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="33"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="10"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="31"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="33"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="31"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="33"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="31"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="7"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="33"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="31"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="7"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="33"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="10"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="31"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="7"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="33"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="31"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="33"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="31"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="33"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="10"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-      <c r="P31" s="31"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="7"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="33"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="10"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="31"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="7"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="33"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="10"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="31"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="7"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="33"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="10"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="31"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="F13:P13"/>
-    <mergeCell ref="F14:P14"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -1932,37 +1926,60 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="F13:P13"/>
+    <mergeCell ref="F14:P14"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C4C04D-F1E3-4E81-BEF1-3C60DD1DEB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439C6AD-C88A-441C-A36E-6D8F3D13DFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="300" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="6345" yWindow="300" windowWidth="21600" windowHeight="11295" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Planification</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>J'ai fais mon analyse dans le rapport</t>
+  </si>
+  <si>
+    <t>Tests unitaires</t>
   </si>
 </sst>
 </file>
@@ -379,22 +382,76 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -406,15 +463,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -425,51 +473,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -810,308 +813,319 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="33" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="34"/>
+      <c r="M2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="36"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="26"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="36"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="36"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="36"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="36"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="34"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="12" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="34"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="21"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1128,17 +1142,6 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1154,50 +1157,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1206,50 +1209,50 @@
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1258,50 +1261,50 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1310,598 +1313,621 @@
       <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="7"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="7"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="7"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="8"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="7"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="7"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="8"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="7"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="7"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="8"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="7"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="7"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="8"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="7"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="7"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="10"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="6"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="10"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="7"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="10"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="7"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="F13:P13"/>
+    <mergeCell ref="F14:P14"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D14:E14"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -1926,60 +1952,37 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="F13:P13"/>
-    <mergeCell ref="F14:P14"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3439C6AD-C88A-441C-A36E-6D8F3D13DFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F01C065-F8FD-411C-9A68-442DF91CF780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="300" windowWidth="21600" windowHeight="11295" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Planification</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Tests unitaires</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>J'ai continué mon analyse dans le rapport</t>
   </si>
 </sst>
 </file>
@@ -379,6 +385,81 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -398,81 +479,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -813,305 +819,305 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="23" t="s">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="24"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="30" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="27" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="26"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="27" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="26"/>
-    </row>
-    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="26"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="30" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="26"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="19"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="26"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="26"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="30" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="26"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="19"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="26"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="26"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="19"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="27" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="34"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="27"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="34"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="30" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="27" t="s">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="36"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -1157,720 +1163,728 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="8"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="33"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46262</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="6"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="31"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="33"/>
+      <c r="D4" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="33"/>
+      <c r="F4" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="8"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="33"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46262</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="6"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="31"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="33"/>
+      <c r="F6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="8"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="33"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46262</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="31"/>
+      <c r="D7" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="31"/>
+      <c r="F7" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="6"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="31"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="8"/>
+      <c r="A8" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="33"/>
+      <c r="F8" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="33"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="6"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="8"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="33"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="6"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="31"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="8"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="6"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="8"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="33"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="6"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="31"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="8"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="33"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="6"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="31"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="8"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="33"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="6"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="31"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="8"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="6"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="31"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="8"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="33"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="6"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="31"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="8"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="33"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="6"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="31"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="8"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="33"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="6"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="31"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="8"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="33"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="6"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="31"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="8"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="33"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="6"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="31"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="8"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="33"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="6"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="31"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="8"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="33"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="6"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="31"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="8"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="33"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="6"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="109">

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F01C065-F8FD-411C-9A68-442DF91CF780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B997E75-8A07-4075-BA5E-C72A7A80D5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>Planification</t>
   </si>
@@ -156,16 +156,37 @@
     <t>Analyse</t>
   </si>
   <si>
-    <t>J'ai fais mon analyse dans le rapport</t>
-  </si>
-  <si>
     <t>Tests unitaires</t>
   </si>
   <si>
-    <t>3h</t>
-  </si>
-  <si>
     <t>J'ai continué mon analyse dans le rapport</t>
+  </si>
+  <si>
+    <t>1h 30</t>
+  </si>
+  <si>
+    <t>J'ai commencé mon analyse dans le rapport</t>
+  </si>
+  <si>
+    <t>J'ai pris du recul sur comment faire mon projet pour continuer mon analyse</t>
+  </si>
+  <si>
+    <t>Reflexion</t>
+  </si>
+  <si>
+    <t>1h30</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>J'ai fais des test pour entrer une plaque d'immatriculation en 2 étapes et j'ai rajouté des vérifications d'erreurs</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>J'ai fais l'affichage du menu et un switch pour faire son choix ce qui va ensuite appeler la méthode définit</t>
   </si>
 </sst>
 </file>
@@ -385,6 +406,57 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -428,57 +500,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -819,319 +840,308 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="32"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="16" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="17"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="23" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="19"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="36"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="36"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="23" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="36"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="20" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="19"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="36"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="19"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="36"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="27"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="19"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="29"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1148,6 +1158,17 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1163,761 +1184,810 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="32" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="33"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46262</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="30" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="31"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="32" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="33"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46262</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="30" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="30" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="31"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="33"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46262</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="31"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46269</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="32" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="33"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="31"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="33"/>
+      <c r="A10" s="4">
+        <v>46276</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="31"/>
+      <c r="A11" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="33"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="31"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="33"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="31"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="33"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="10"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="31"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="33"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="31"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="33"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="31"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="7"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="33"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="31"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="7"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="33"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="10"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="31"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="7"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="33"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="31"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="33"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="31"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="33"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="10"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="36"/>
-      <c r="P31" s="31"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="7"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="33"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="10"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="31"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="7"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="33"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="10"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="31"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="7"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="33"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="10"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="36"/>
-      <c r="P37" s="31"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F9:P9"/>
     <mergeCell ref="F10:P10"/>
@@ -1942,62 +2012,38 @@
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B997E75-8A07-4075-BA5E-C72A7A80D5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3BF44E-B420-4395-AF9F-6C23B1C47074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="35160" yWindow="1305" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Planification</t>
   </si>
@@ -186,7 +186,24 @@
     <t>code</t>
   </si>
   <si>
-    <t>J'ai fais l'affichage du menu et un switch pour faire son choix ce qui va ensuite appeler la méthode définit</t>
+    <t>J'ai fais l'affichage du menu et un switch pour faire son choix ce qui va ensuite appeler la méthode définit puis j'ai commencé 
+la methode pour faire rentrer une voiture mais elle avais quelques problèmes et était en phase de test</t>
+  </si>
+  <si>
+    <t>J'ai commencé par corriger les problèmes que j'avais pour l'entrée des voitures qui consistaient a:
+ le matricule faux s'affichait quand meme quand j'en remplissais un correctement et aucun système de vérification que le matricule n'aie que des chiffres</t>
+  </si>
+  <si>
+    <t>45min</t>
+  </si>
+  <si>
+    <t>Révision</t>
+  </si>
+  <si>
+    <t>Autour de la table a poser des questions et écouter les expliquations</t>
+  </si>
+  <si>
+    <t>Début de code pour choisir une place pour y mettre la voiture et que la place soit occupée</t>
   </si>
 </sst>
 </file>
@@ -400,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -409,98 +426,104 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -840,308 +863,319 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="33" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="34"/>
+      <c r="M2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="36"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="26"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="36"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="36"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="36"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="36"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="36"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="34"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="12" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="19"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="34"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="21"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1158,17 +1192,6 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1181,53 +1204,54 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="16" max="16" width="37.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1236,50 +1260,50 @@
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1288,50 +1312,50 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1340,50 +1364,50 @@
       <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="7"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46269</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="8"/>
+      <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1392,578 +1416,625 @@
       <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46276</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="8"/>
+      <c r="D10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46276</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
+      <c r="A13" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
+      <c r="A14" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="7"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="8"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="7"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="7"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="8"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="7"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="7"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="8"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="7"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="7"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="8"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="7"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="7"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="10"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="6"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="10"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="7"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="10"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="7"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="F13:P13"/>
+    <mergeCell ref="F14:P14"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D14:E14"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -1988,60 +2059,37 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="F13:P13"/>
-    <mergeCell ref="F14:P14"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F750F75-1D69-4BA3-BE49-C3AFCE23E9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1CAB30-2627-4BA0-8A04-ADEF1270115C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="34470" yWindow="1575" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>Planification</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>Analyse comment je vais faire la sortie de la voiture et afficher le parking</t>
+  </si>
+  <si>
+    <t>1h20</t>
+  </si>
+  <si>
+    <t>J'ai fait générer unn ticket a l'entrée et a la sortie afficher le ticket avec l'arrivée la sortie et la durée qui determine le prix avec un tarif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'ai fais compter le nombre de ticket et le total des prix des tickets pour faire les statistiques </t>
   </si>
 </sst>
 </file>
@@ -441,19 +450,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -462,7 +474,58 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -474,15 +537,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -493,51 +547,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -878,308 +887,319 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="34"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="35" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="36"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="38"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="38"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="38"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="38"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="28"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="38"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="28"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="38"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="28"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="38"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="28"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="38"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="28"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="38"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="17" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="36"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="21"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="36"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="21"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="36"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="21"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="36"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="17" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1196,17 +1216,6 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1223,50 +1232,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="10"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="9"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1275,50 +1284,50 @@
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="10"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="9"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1327,50 +1336,50 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1379,50 +1388,50 @@
       <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="7"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46269</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="9"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1431,50 +1440,50 @@
       <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46269</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="9"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1483,50 +1492,50 @@
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46276</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="9"/>
     </row>
     <row r="13" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1535,50 +1544,50 @@
       <c r="B13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46283</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="12" t="s">
+      <c r="E14" s="9"/>
+      <c r="F14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="9"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1587,50 +1596,50 @@
       <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46283</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="9"/>
+      <c r="F16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="9"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -1639,50 +1648,50 @@
       <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="7"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46290</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="9"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -1691,424 +1700,457 @@
       <c r="B19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="7"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="7"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
+      <c r="A20" s="4">
+        <v>46297</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="9"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="7"/>
+      <c r="A21" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="9"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="7"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="9"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="7"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="7"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="9"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="9"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="9"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="7"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="10"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="9"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="6"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="10"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="9"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="7"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="10"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="9"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="7"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="6"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="10"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="9"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
+      <c r="C39" s="6"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="7"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="115">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F39:P39"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F38:P38"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="F13:P13"/>
+    <mergeCell ref="F14:P14"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -2133,60 +2175,43 @@
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="F13:P13"/>
-    <mergeCell ref="F14:P14"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F39:P39"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F38:P38"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1CAB30-2627-4BA0-8A04-ADEF1270115C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB3A6D1-1861-4D20-A461-D8DA28C2F910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34470" yWindow="1575" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
   <si>
     <t>Planification</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t xml:space="preserve">J'ai fais compter le nombre de ticket et le total des prix des tickets pour faire les statistiques </t>
+  </si>
+  <si>
+    <t>par ex</t>
+  </si>
+  <si>
+    <t>Correction de plusieurs problèmes avec l'acceptation de mes methodes (par ex: le canton je pouvais mettre "v1" ou " vd" j'ai du rajouter trim et un char.isLetter et aussi la meme chose pour les matricules) avec Raphaël</t>
   </si>
 </sst>
 </file>
@@ -450,6 +456,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -460,12 +469,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -474,6 +477,39 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -517,36 +553,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -887,319 +893,308 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="34"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="25" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="26"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="32" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="28"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="38"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="28"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="38"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="28"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="38"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="32" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="28"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="38"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="32" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="38"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="28"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="38"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="28"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="38"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="28"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="38"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="28"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="38"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="29" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="28"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="38"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="29" t="s">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="36"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="36"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="32" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="36"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="21"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="29" t="s">
+      <c r="B16" s="29"/>
+      <c r="C16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="36"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="21"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="29" t="s">
+      <c r="A17" s="30"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="38"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1216,6 +1211,17 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1228,54 +1234,54 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="16" max="16" width="37.28515625" customWidth="1"/>
+    <col min="16" max="16" width="82.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1284,50 +1290,50 @@
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1336,50 +1342,50 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1388,50 +1394,50 @@
       <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46269</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="10"/>
+      <c r="D8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1440,50 +1446,50 @@
       <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46269</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="10"/>
+      <c r="D10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1492,50 +1498,50 @@
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="7"/>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46276</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="10"/>
+      <c r="D12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1544,50 +1550,50 @@
       <c r="B13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="7"/>
       <c r="D13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="12" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46283</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="13" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1596,50 +1602,50 @@
       <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46283</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="10"/>
+      <c r="D16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="7" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="10"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -1648,50 +1654,50 @@
       <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="7"/>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46290</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="10"/>
+      <c r="D18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="10"/>
+      <c r="F18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -1700,50 +1706,50 @@
       <c r="B19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="7"/>
       <c r="D19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="7"/>
       <c r="F19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46297</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="10"/>
+      <c r="D20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="7" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -1752,381 +1758,420 @@
       <c r="B21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="7"/>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="9"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="7"/>
+    </row>
+    <row r="22" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46297</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
+      <c r="C23" s="7"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="7"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="10"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="7"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="10"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+      <c r="C27" s="7"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
+      <c r="E29" s="7"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="10"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
+      <c r="E31" s="7"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="7"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="10"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="7"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="10"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+      <c r="C35" s="7"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="7"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="10"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
+      <c r="C37" s="7"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
+      <c r="E37" s="7"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="7"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="10"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
+      <c r="E39" s="7"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="115">
-    <mergeCell ref="F39:P39"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F38:P38"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F9:P9"/>
     <mergeCell ref="F12:P12"/>
@@ -2151,67 +2196,36 @@
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F39:P39"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F38:P38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/T-I320-LucaPardo-planification-JDT.xlsx
+++ b/doc/T-I320-LucaPardo-planification-JDT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2ème année\1er trimestre\I320-ACD\projet\I320-Projet\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB3A6D1-1861-4D20-A461-D8DA28C2F910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B487AE3-0129-4D96-A329-538367AA76BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9576A379-5D86-4DEE-A374-748D0B7984AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planification" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>Planification</t>
   </si>
@@ -230,10 +230,22 @@
     <t xml:space="preserve">J'ai fais compter le nombre de ticket et le total des prix des tickets pour faire les statistiques </t>
   </si>
   <si>
-    <t>par ex</t>
-  </si>
-  <si>
     <t>Correction de plusieurs problèmes avec l'acceptation de mes methodes (par ex: le canton je pouvais mettre "v1" ou " vd" j'ai du rajouter trim et un char.isLetter et aussi la meme chose pour les matricules) avec Raphaël</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>(maison) J'ai fais les statistiques du jour et ai modifié mon historique des transactions.</t>
+  </si>
+  <si>
+    <t>doc</t>
+  </si>
+  <si>
+    <t>30min</t>
+  </si>
+  <si>
+    <t>J'ai complété mon rapport un minimum</t>
   </si>
 </sst>
 </file>
@@ -456,19 +468,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -477,7 +492,58 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -489,15 +555,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -508,51 +565,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -893,308 +905,319 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="34"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="35" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="36"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="38"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="38"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="38"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="38"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="28"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28"/>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="38"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="28"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="38"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="28"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="38"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="28"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="38"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="28"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="38"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="17" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="36"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="21"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="36"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="21"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="36"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="21"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="36"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="17" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="L13:M17"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A2:B3"/>
@@ -1211,17 +1234,6 @@
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="L13:M17"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1238,50 +1250,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="10"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="9"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1290,50 +1302,50 @@
       <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46262</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="10"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="9"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1342,50 +1354,50 @@
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46262</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1394,50 +1406,50 @@
       <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="7"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46269</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="9"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1446,50 +1458,50 @@
       <c r="B9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46269</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="9"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -1498,50 +1510,50 @@
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46276</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="9"/>
     </row>
     <row r="13" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1550,50 +1562,50 @@
       <c r="B13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46283</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="12" t="s">
+      <c r="E14" s="9"/>
+      <c r="F14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="9"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -1602,50 +1614,50 @@
       <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46283</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="9"/>
+      <c r="F16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="9"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -1654,50 +1666,50 @@
       <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="7"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46290</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="9"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -1706,50 +1718,50 @@
       <c r="B19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="7"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="7"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46297</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="9"/>
+      <c r="D20" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="8" t="s">
+      <c r="E20" s="9"/>
+      <c r="F20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="9"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -1758,396 +1770,429 @@
       <c r="B21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="7"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46297</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="9"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
+      <c r="A24" s="4">
+        <v>46297</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="9"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="7"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="7"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="9"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="9"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="9"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="7"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="10"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="9"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="6"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="10"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="9"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="7"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="7"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="6"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="10"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="9"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="7"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="7"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="6"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="10"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="9"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
+      <c r="C39" s="6"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="7"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="115">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F10:P10"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F39:P39"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F32:P32"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="F34:P34"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F35:P35"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="F37:P37"/>
+    <mergeCell ref="F38:P38"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="F24:P24"/>
+    <mergeCell ref="F25:P25"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="F13:P13"/>
+    <mergeCell ref="F14:P14"/>
+    <mergeCell ref="F15:P15"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -2172,60 +2217,43 @@
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="F13:P13"/>
-    <mergeCell ref="F14:P14"/>
-    <mergeCell ref="F15:P15"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="F24:P24"/>
-    <mergeCell ref="F25:P25"/>
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F39:P39"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F32:P32"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="F34:P34"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F35:P35"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="F37:P37"/>
-    <mergeCell ref="F38:P38"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F2:P2"/>
+    <mergeCell ref="F3:P3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
